--- a/VerveStacks_ZWE_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ZWE_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZWE_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99FF862-EEF1-49EB-8DBC-7CF2644BCC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD224DC8-B4EF-4B04-9617-126F3924AD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -958,22 +958,22 @@
                   <c:v>10.610000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.368600000000002</c:v>
+                  <c:v>14.960100000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16.021100000000001</c:v>
+                  <c:v>19.098000000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.310200000000002</c:v>
+                  <c:v>29.177500000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>23.235900000000001</c:v>
+                  <c:v>35.6496</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>27.479900000000001</c:v>
+                  <c:v>54.323200000000007</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>35.225200000000001</c:v>
+                  <c:v>60.370900000000013</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6041,7 +6041,7 @@
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.45">
       <c r="D3" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K3" s="10">
         <v>300</v>
@@ -6067,13 +6067,13 @@
         <v>82</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.45">
       <c r="D5" s="1" t="str">
         <f>VLOOKUP(D3,$C$9:$E$999,2,FALSE)</f>
-        <v>base</v>
+        <v>high</v>
       </c>
       <c r="E5" s="1">
         <f>VLOOKUP(D3,$C$9:$E$999,3,FALSE)</f>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="H14" s="3" t="str">
         <f>VLOOKUP($D$5,$N$3:$O$5,2,FALSE)</f>
-        <v>C4</v>
+        <v>C7</v>
       </c>
       <c r="I14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$E$5,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
@@ -6371,27 +6371,27 @@
       </c>
       <c r="J14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="K14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="L14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="M14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>2.19</v>
+        <v>3.36</v>
       </c>
       <c r="N14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>2.59</v>
+        <v>5.12</v>
       </c>
       <c r="O14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>3.32</v>
+        <v>5.69</v>
       </c>
       <c r="T14" s="8">
         <f>S11</f>
@@ -6399,27 +6399,27 @@
       </c>
       <c r="U14" s="8">
         <f t="shared" ref="U14:Z14" si="4">$S$11*J14</f>
-        <v>13.368600000000002</v>
+        <v>14.960100000000001</v>
       </c>
       <c r="V14" s="8">
         <f t="shared" si="4"/>
-        <v>16.021100000000001</v>
+        <v>19.098000000000003</v>
       </c>
       <c r="W14" s="8">
         <f t="shared" si="4"/>
-        <v>19.310200000000002</v>
+        <v>29.177500000000002</v>
       </c>
       <c r="X14" s="8">
         <f t="shared" si="4"/>
-        <v>23.235900000000001</v>
+        <v>35.6496</v>
       </c>
       <c r="Y14" s="8">
         <f t="shared" si="4"/>
-        <v>27.479900000000001</v>
+        <v>54.323200000000007</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="4"/>
-        <v>35.225200000000001</v>
+        <v>60.370900000000013</v>
       </c>
       <c r="AG14">
         <v>6</v>
@@ -6464,27 +6464,27 @@
       </c>
       <c r="J15" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="K15" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>3</v>
+        <v>3.31</v>
       </c>
       <c r="L15" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>6.36</v>
+        <v>11.21</v>
       </c>
       <c r="M15" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>10.94</v>
+        <v>7.67</v>
       </c>
       <c r="N15" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>16.899999999999999</v>
+        <v>20.170000000000002</v>
       </c>
       <c r="O15" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>20.47</v>
+        <v>15.86</v>
       </c>
       <c r="AG15">
         <v>7</v>
@@ -6616,62 +6616,62 @@
       </c>
       <c r="I18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="S18" s="10" t="s">
         <v>16</v>
       </c>
       <c r="T18" s="6">
         <f t="shared" ref="T18:Z20" si="7">I18*T$14</f>
-        <v>0</v>
+        <v>0.10610000000000001</v>
       </c>
       <c r="U18" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.14960100000000001</v>
       </c>
       <c r="V18" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.19098000000000004</v>
       </c>
       <c r="W18" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.58355000000000001</v>
       </c>
       <c r="X18" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.71299199999999996</v>
       </c>
       <c r="Y18" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.6296960000000003</v>
       </c>
       <c r="Z18" s="6">
         <f t="shared" si="7"/>
-        <v>0.35225200000000001</v>
+        <v>1.8111270000000004</v>
       </c>
       <c r="AA18" t="s">
         <v>17</v>
@@ -6697,62 +6697,62 @@
       </c>
       <c r="I19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="J19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="K19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.34</v>
+        <v>0.49</v>
       </c>
       <c r="L19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.35</v>
+        <v>0.52</v>
       </c>
       <c r="M19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="N19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="O19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="S19" s="10" t="s">
         <v>19</v>
       </c>
       <c r="T19" s="6">
         <f t="shared" si="7"/>
-        <v>4.7745000000000006</v>
+        <v>5.3050000000000006</v>
       </c>
       <c r="U19" s="6">
         <f t="shared" si="7"/>
-        <v>5.8821840000000014</v>
+        <v>7.7792520000000005</v>
       </c>
       <c r="V19" s="6">
         <f t="shared" si="7"/>
-        <v>5.4471740000000004</v>
+        <v>9.3580200000000016</v>
       </c>
       <c r="W19" s="6">
         <f t="shared" si="7"/>
-        <v>6.7585700000000006</v>
+        <v>15.172300000000002</v>
       </c>
       <c r="X19" s="6">
         <f t="shared" si="7"/>
-        <v>7.667847000000001</v>
+        <v>17.8248</v>
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="7"/>
-        <v>10.442362000000001</v>
+        <v>27.161600000000004</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="7"/>
-        <v>12.681072</v>
+        <v>28.978032000000006</v>
       </c>
       <c r="AA19" t="s">
         <v>17</v>
@@ -6777,62 +6777,62 @@
       </c>
       <c r="I20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="J20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="K20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.56999999999999995</v>
+        <v>0.47</v>
       </c>
       <c r="L20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="M20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="N20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="O20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="S20" s="10" t="s">
         <v>22</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="7"/>
-        <v>5.7294000000000009</v>
+        <v>5.1989000000000001</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="7"/>
-        <v>7.219044000000002</v>
+        <v>6.8816460000000008</v>
       </c>
       <c r="V20" s="6">
         <f t="shared" si="7"/>
-        <v>9.132026999999999</v>
+        <v>8.9760600000000004</v>
       </c>
       <c r="W20" s="6">
         <f t="shared" si="7"/>
-        <v>11.779222000000001</v>
+        <v>13.421650000000001</v>
       </c>
       <c r="X20" s="6">
         <f t="shared" si="7"/>
-        <v>14.173899</v>
+        <v>16.755312</v>
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="7"/>
-        <v>14.839146000000001</v>
+        <v>26.075136000000004</v>
       </c>
       <c r="Z20" s="6">
         <f t="shared" si="7"/>
-        <v>18.669356000000001</v>
+        <v>29.581741000000005</v>
       </c>
       <c r="AA20" t="s">
         <v>17</v>
@@ -6861,27 +6861,27 @@
       </c>
       <c r="J21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="M21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="N21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="O21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="S21" s="10" t="s">
         <v>24</v>
@@ -6935,27 +6935,27 @@
       </c>
       <c r="U22" s="6">
         <f t="shared" si="9"/>
-        <v>0.1612720000000003</v>
+        <v>0.19310199999999966</v>
       </c>
       <c r="V22" s="6">
         <f t="shared" si="9"/>
-        <v>1.3357990000000015</v>
+        <v>0.65782000000000096</v>
       </c>
       <c r="W22" s="6">
         <f t="shared" si="9"/>
-        <v>0.66630799999999724</v>
+        <v>0.47744999999999749</v>
       </c>
       <c r="X22" s="6">
         <f t="shared" si="9"/>
-        <v>1.2880539999999989</v>
+        <v>0.96338800000000191</v>
       </c>
       <c r="Y22" s="6">
         <f t="shared" si="9"/>
-        <v>2.0922919999999969</v>
+        <v>0.98036400000000157</v>
       </c>
       <c r="Z22" s="6">
         <f t="shared" si="9"/>
-        <v>3.7686719999999987</v>
+        <v>1.7050270000000083</v>
       </c>
       <c r="AA22" t="s">
         <v>17</v>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="O48">
         <f>VLOOKUP($H$14,$AK$9:$AM$15,3,FALSE)*I48</f>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R48">
         <f>HLOOKUP($G48&amp;"_"&amp;R$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
